--- a/Test Cases By Mansib.xlsx
+++ b/Test Cases By Mansib.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Desktop\Mansib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DC1F30-699C-4B41-A966-4D2288BB21C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EDE7F48-F2B6-4FCD-B438-146BEEDA94FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="6" xr2:uid="{17219D56-72BD-441D-95A4-13C60CFAC7D7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="3" xr2:uid="{17219D56-72BD-441D-95A4-13C60CFAC7D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Version History" sheetId="9" r:id="rId1"/>
@@ -23,7 +23,10 @@
     <sheet name="CheckOut Page" sheetId="7" r:id="rId8"/>
     <sheet name="My Account Page" sheetId="8" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <externalReferences>
+    <externalReference r:id="rId10"/>
+  </externalReferences>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,6 +38,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -42,7 +47,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="312">
+  <si>
+    <t>Project Name (Client Name)</t>
+  </si>
+  <si>
+    <t>Yusha</t>
+  </si>
+  <si>
+    <t>Prepared By</t>
+  </si>
+  <si>
+    <t>Mansib</t>
+  </si>
   <si>
     <t>Test Case ID</t>
   </si>
@@ -62,6 +79,9 @@
     <t>Test Data</t>
   </si>
   <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
     <t>Actual Result</t>
   </si>
   <si>
@@ -77,22 +97,11 @@
     <t>TC_LF_001</t>
   </si>
   <si>
+    <t>(TS_001) 
+Login Functionality</t>
+  </si>
+  <si>
     <t>Validate logging into the Application using valid credentials</t>
-  </si>
-  <si>
-    <t>TC_LF_002</t>
-  </si>
-  <si>
-    <t>TC_LF_003</t>
-  </si>
-  <si>
-    <t>Validate logging into the Application without providing any credentials</t>
-  </si>
-  <si>
-    <t>Not Applicable</t>
-  </si>
-  <si>
-    <t>Expected Result</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open the Application URL (https://yusha.com.bd) in any supported Browser
@@ -106,7 +115,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve"> Phone Number - 01786492383</t>
+    <t xml:space="preserve"> Phone Number - 01534727582</t>
   </si>
   <si>
     <t>1.User should get logged in and taken to the 'Home' page
@@ -115,6 +124,12 @@
   </si>
   <si>
     <t>Passed</t>
+  </si>
+  <si>
+    <t>TC_LF_002</t>
+  </si>
+  <si>
+    <t>Validate logging into the Application using invalid credentials ( Invalid PhoneNumber)</t>
   </si>
   <si>
     <t>Open the Application URL (https://yusha.com.bd) in any supported Browser</t>
@@ -132,11 +147,10 @@
     <t>1. Warning message with the text: ' Phone number must start with 01 and be 11 digits ' should be displayed</t>
   </si>
   <si>
-    <t>Validate logging into the Application using invalid credentials ( Invalid PhoneNumber)</t>
-  </si>
-  <si>
-    <t>(TS_001) 
-Login Functionality</t>
+    <t>TC_LF_003</t>
+  </si>
+  <si>
+    <t>Validate logging into the Application without providing any credentials</t>
   </si>
   <si>
     <t xml:space="preserve">1. Click on 'Sign in/Sign Up' On the top Right
@@ -145,10 +159,20 @@
 </t>
   </si>
   <si>
+    <t>Not Applicable</t>
+  </si>
+  <si>
     <t>1. Warning message with the text ' Phone number is required ' should be displayed</t>
   </si>
   <si>
     <t>TC_LG_001</t>
+  </si>
+  <si>
+    <t>(TS_002)
+Logout Functionality</t>
+  </si>
+  <si>
+    <t>Validate Logging out by selecting Logout option from Home Page :'Account Name' dropmenu</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open the Application URL
@@ -156,9 +180,6 @@
 </t>
   </si>
   <si>
-    <t>Validate Logging out by selecting Logout option from Home Page :'Account Name' dropmenu</t>
-  </si>
-  <si>
     <t>1. Click on 'Account Name' Dropmenu Top right.
 2. Click on 'Logout' button.</t>
   </si>
@@ -166,16 +187,12 @@
     <t>1. User should be taken to the Home page</t>
   </si>
   <si>
-    <t>(TS_002)
-Logout Functionality</t>
+    <t xml:space="preserve">Validate Logging out by selecting Logout option from Home Page :Menu
+</t>
   </si>
   <si>
     <t>1. Click on 'Menu' Top Left.
 2. Click on 'Logout' button.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validate Logging out by selecting Logout option from Home Page :Menu
-</t>
   </si>
   <si>
     <t xml:space="preserve">Validate Logging out by selecting Logout option from My Account Page
@@ -193,94 +210,23 @@
     <t>TC_HP_001</t>
   </si>
   <si>
-    <t>1. Open the Application URL</t>
+    <t xml:space="preserve">
+Home Page</t>
+  </si>
+  <si>
+    <t>Validate navigating to Home page from any page of the Applcation using Logo</t>
+  </si>
+  <si>
+    <t>1. Open the Application URL and navigate to any page of the Application</t>
+  </si>
+  <si>
+    <t>1. Click on the Logo 'YUSHA' in  application</t>
   </si>
   <si>
     <t>1. User should be taken to Home page</t>
   </si>
   <si>
     <t>TC_HP_002</t>
-  </si>
-  <si>
-    <t>TC_HP_003</t>
-  </si>
-  <si>
-    <t>Validate navigating to Home page from any page of the Applcation using Logo</t>
-  </si>
-  <si>
-    <t>1. Open the Application URL and navigate to any page of the Application</t>
-  </si>
-  <si>
-    <t>TC_HP_004</t>
-  </si>
-  <si>
-    <t>TC_HP_005</t>
-  </si>
-  <si>
-    <t>TC_HP_006</t>
-  </si>
-  <si>
-    <t>TC_HP_007</t>
-  </si>
-  <si>
-    <t>TC_HP_008</t>
-  </si>
-  <si>
-    <t>TC_HP_009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the Application URL in any supported browser </t>
-  </si>
-  <si>
-    <t>1. Check the UI of the functionality related to 'Home' page (Validate ER-1)</t>
-  </si>
-  <si>
-    <t>TC_HP_010</t>
-  </si>
-  <si>
-    <t>1. Check the 'Home' page functionality in all the supported environments (Validate ER-1)</t>
-  </si>
-  <si>
-    <t>TC_ATC_001</t>
-  </si>
-  <si>
-    <t>(TS_008)
-Add to Cart</t>
-  </si>
-  <si>
-    <t>TC_ATC_002</t>
-  </si>
-  <si>
-    <t>Validate adding the product to Cart from 'Wish List' Page</t>
-  </si>
-  <si>
-    <t>1. Open the Application URL and Login
-2. A product is added to Wish List page  - &lt;Refer Test Data&gt;</t>
-  </si>
-  <si>
-    <t>TC_ATC_003</t>
-  </si>
-  <si>
-    <t>Validate adding the product to Cart from Search Results Page</t>
-  </si>
-  <si>
-    <t>TC_ATC_004</t>
-  </si>
-  <si>
-    <t>TC_ATC_005</t>
-  </si>
-  <si>
-    <t>TC_ATC_006</t>
-  </si>
-  <si>
-    <t>(TS_007)
-Product Display Page</t>
-  </si>
-  <si>
-    <t>Validate Product Categories should be displayed in the Home Page</t>
-  </si>
-  <si>
-    <t>Validate Max(75) Latest products with (See All Products) button should be displayed in the Home Page</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -288,41 +234,119 @@
 </t>
   </si>
   <si>
+    <t>1. Open the Application URL</t>
+  </si>
+  <si>
+    <t>1. Check the Carousel images and slider options on the displayed Home page.
+2. Click any banner Images</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Correct Banner Images should be displayed. 
+2. Banner Images should automatically slide
+3. By clicking images , navigates to specific product page
+4. By clicking slide arrow button images changes
+</t>
+  </si>
+  <si>
+    <t>TC_HP_003</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 Validate HeroBanner in the Home page
 </t>
   </si>
   <si>
+    <t>1. Check the HeroBanner images on the displayed Home page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Correct Banner Images should be displayed. 
+2. By clicking images , navigates to specific product page
+</t>
+  </si>
+  <si>
+    <t>TC_HP_004</t>
+  </si>
+  <si>
+    <t>Validate Product Categories should be displayed in the Home Page</t>
+  </si>
+  <si>
+    <t>1. Check the Product Categories section in the displayed Home page.
+2.Click category icon
+3.Observe Category Page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Product categories Section with icon Should display.
+2. By clicking category icon , navigates to specific category with products page
+3.Particular Category Products Should Show
+</t>
+  </si>
+  <si>
+    <t>TC_HP_005</t>
+  </si>
+  <si>
+    <t>Validate Max(75) Latest products with (See All Products) button should be displayed in the Home Page</t>
+  </si>
+  <si>
+    <t>1. Check the Latest Products section in the displayed Home page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. All 75 (Max) products should show by clicking See  All button
+</t>
+  </si>
+  <si>
+    <t>TC_HP_006</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 Validate the UI of 'Home' page functionality
 </t>
   </si>
   <si>
+    <t xml:space="preserve">1. Open the Application URL in any supported browser </t>
+  </si>
+  <si>
+    <t>1. Check the UI of the functionality related to 'Home' page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Proper UI adhering to the UI checklist should be displayed for the 'Home' page functionality
+</t>
+  </si>
+  <si>
+    <t>TC_HP_007</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 Validate the 'Home' page functionality in all the supported environments
 </t>
   </si>
   <si>
-    <t>1. Click on the Logo 'YUSHA' in  application</t>
-  </si>
-  <si>
-    <t>1. Check the Carousel images and slider options on the displayed Home page.</t>
-  </si>
-  <si>
-    <t>1. Check the HeroBanner images on the displayed Home page</t>
-  </si>
-  <si>
-    <t>1. Check the Product Categories section in the displayed Home page</t>
-  </si>
-  <si>
-    <t>1. Check the Latest Products section in the displayed Home page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Home Page</t>
-  </si>
-  <si>
-    <t>Product Name: Wrist Pendant</t>
+    <t>1. Check the 'Home' page functionality in all the supported environments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 'Home' page functionality should work correctly in all the supported environments
+</t>
+  </si>
+  <si>
+    <t>TC_HP_008</t>
+  </si>
+  <si>
+    <t>TC_HP_009</t>
+  </si>
+  <si>
+    <t>TC_HP_010</t>
+  </si>
+  <si>
+    <t>TC_ATC_001</t>
+  </si>
+  <si>
+    <t>(TS_008)
+Add to Cart</t>
+  </si>
+  <si>
+    <t>Validate adding the product to Cart from Search Results Page</t>
+  </si>
+  <si>
+    <t>1. Open the Application URL and Login</t>
   </si>
   <si>
     <t xml:space="preserve">1. Enter any existing Product name into the Search text box field - &lt;Refer Test Data&gt;
@@ -332,11 +356,21 @@
 </t>
   </si>
   <si>
+    <t>Product Name: Wrist Pendant</t>
+  </si>
+  <si>
     <t>1. Success message with text - 'Successfully added to  cart!' should be displayed
 2. Product should be successfully displayed in the 'Shopping Cart' page</t>
   </si>
   <si>
-    <t>1. Open the Application URL and Login</t>
+    <t>TC_ATC_002</t>
+  </si>
+  <si>
+    <t>Validate adding the product to Cart from 'Wish List' Page</t>
+  </si>
+  <si>
+    <t>1. Open the Application URL and Login
+2. A product is added to Wish List page  - &lt;Refer Test Data&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -352,37 +386,21 @@
 </t>
   </si>
   <si>
-    <t>Validate the UI of 'Add to Cart' funtionality</t>
-  </si>
-  <si>
-    <t>Validate the 'Add to Cart' page functionality in all the supported environments</t>
-  </si>
-  <si>
-    <t>1. Open the Application URL in any supported browser</t>
-  </si>
-  <si>
-    <t>1. Check the UI of the functioanality related to 'Add to Cart' (Validate ER-1)</t>
-  </si>
-  <si>
-    <t>1. Check the 'Add to Cart' functionality in all the supported environments (Validate ER-1)</t>
-  </si>
-  <si>
-    <t>1. 'Add to Cart' functionality should work correctly in all the supported environments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Proper UI adhering to the UI checklist should be displayed for the 'Add to Cart' functionality
-</t>
+    <t>TC_ATC_003</t>
   </si>
   <si>
     <t>Validate adding the product to Cart from the Products displayed in the 'Featured' section of Home page</t>
-  </si>
-  <si>
-    <t>Validate adding the product to Cart from the Products displayed in the category or sub-category page</t>
   </si>
   <si>
     <t>1.Click any Product Item.
 2. Click on 'Add to Cart' button on the product that is displayed in the 'Featured' section of the Home page 
 2. Click on 'Add to Cart' button in the displayed 'Product Display' page.</t>
+  </si>
+  <si>
+    <t>TC_ATC_004</t>
+  </si>
+  <si>
+    <t>Validate adding the product to Cart from the Products displayed in the category or sub-category page</t>
   </si>
   <si>
     <t xml:space="preserve">1. Hover the mouse on Top Nav'
@@ -392,7 +410,35 @@
 </t>
   </si>
   <si>
-    <t>&lt;&lt; Test Scenarios</t>
+    <t>TC_ATC_005</t>
+  </si>
+  <si>
+    <t>Validate the UI of 'Add to Cart' funtionality</t>
+  </si>
+  <si>
+    <t>1. Open the Application URL in any supported browser</t>
+  </si>
+  <si>
+    <t>1. Check the UI of the functioanality related to 'Add to Cart' (Validate ER-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Proper UI adhering to the UI checklist should be displayed for the 'Add to Cart' functionality
+</t>
+  </si>
+  <si>
+    <t>TC_ATC_006</t>
+  </si>
+  <si>
+    <t>Validate the 'Add to Cart' page functionality in all the supported environments</t>
+  </si>
+  <si>
+    <t>1. Check the 'Add to Cart' functionality in all the supported environments (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>1. 'Add to Cart' functionality should work correctly in all the supported environments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected Result </t>
   </si>
   <si>
     <t>TC_WL_002</t>
@@ -402,532 +448,10 @@
 Wish List</t>
   </si>
   <si>
+    <t>Validate adding a product to 'Wish List' page from the Search Results page</t>
+  </si>
+  <si>
     <t xml:space="preserve">1. Open the Application URL and login </t>
-  </si>
-  <si>
-    <t>TC_WL_003</t>
-  </si>
-  <si>
-    <t>Validate adding a product to 'Wish List' page from the Product that is displayed in the 'Featured' section of 'Home' page</t>
-  </si>
-  <si>
-    <t>1. Open the Application URL and login</t>
-  </si>
-  <si>
-    <t>TC_WL_004</t>
-  </si>
-  <si>
-    <t>Validate adding the product to Wish List from the Products displayed in the category or sub-category page</t>
-  </si>
-  <si>
-    <t>TC_WL_005</t>
-  </si>
-  <si>
-    <t>Validate adding a product to 'Wish List' page from the Search Results page</t>
-  </si>
-  <si>
-    <t>TC_WL_006</t>
-  </si>
-  <si>
-    <t>TC_WL_007</t>
-  </si>
-  <si>
-    <t>Validate navigating to 'My Wish List' page using the 'Wish List' header option</t>
-  </si>
-  <si>
-    <t>TC_WL_008</t>
-  </si>
-  <si>
-    <t>TC_WL_009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validate navigating to 'My Wish List' page from the 'My Account' page </t>
-  </si>
-  <si>
-    <t>TC_WL_010</t>
-  </si>
-  <si>
-    <t>TC_WL_011</t>
-  </si>
-  <si>
-    <t>TC_WL_012</t>
-  </si>
-  <si>
-    <t>TC_WL_013</t>
-  </si>
-  <si>
-    <t>Validate the 'My Wish List' page when there are no products added</t>
-  </si>
-  <si>
-    <t>TC_WL_014</t>
-  </si>
-  <si>
-    <t>Validate the 'My Wish List' page when only one product is added to it</t>
-  </si>
-  <si>
-    <t>1. Open the Application URL and login
-2. One product is added to 'My Wish List' page</t>
-  </si>
-  <si>
-    <t>Validate the removing the Product  from 'My Wish List' page</t>
-  </si>
-  <si>
-    <t>Validate adding the multiple products to the 'My Wish List' page</t>
-  </si>
-  <si>
-    <t>1. Open the Application URL and login
-2. Add multiple products to 'My Wish List' page</t>
-  </si>
-  <si>
-    <t>Validate adding duplicate products to 'My Wish List' page</t>
-  </si>
-  <si>
-    <t>Validate the UI of 'Wish List' funtionality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected Result </t>
-  </si>
-  <si>
-    <t>TC_PDP_001</t>
-  </si>
-  <si>
-    <t>TC_PDP_002</t>
-  </si>
-  <si>
-    <t>Validate that Product Name, Brand and Product Code are displayed in the Product Display Page</t>
-  </si>
-  <si>
-    <t>TC_PDP_003</t>
-  </si>
-  <si>
-    <t>Validate the availabilty status of the Product in the Product Display Page</t>
-  </si>
-  <si>
-    <t>TC_PDP_004</t>
-  </si>
-  <si>
-    <t>Validate the Price of the Product with and without tax is displayed in the Product Display Page</t>
-  </si>
-  <si>
-    <t>TC_PDP_005</t>
-  </si>
-  <si>
-    <t>Validate the default quanity for the Product is displayed as 1 in the Product Display Page, when there is no minimum quantity set for the Product</t>
-  </si>
-  <si>
-    <t>TC_PDP_006</t>
-  </si>
-  <si>
-    <t>Validate the negative quantity or zero quantity or null quantity should not be allowed in the Product Display Page</t>
-  </si>
-  <si>
-    <t>TC_PDP_007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validate the Product having the minimum quanitity set </t>
-  </si>
-  <si>
-    <t>TC_PDP_008</t>
-  </si>
-  <si>
-    <t>Validate the description of the Product in the Product Display Page</t>
-  </si>
-  <si>
-    <t>TC_PDP_009</t>
-  </si>
-  <si>
-    <t>Validate the specifications of the Product in the Product Display Page</t>
-  </si>
-  <si>
-    <t>TC_PDP_010</t>
-  </si>
-  <si>
-    <t>Validate the User is able to write a review for the Product from the 'Reviews' tab of Product Display Page</t>
-  </si>
-  <si>
-    <t>TC_PDP_011</t>
-  </si>
-  <si>
-    <t>Validate the 'Reviews' tab when there are no reviews or zero reviews added</t>
-  </si>
-  <si>
-    <t>TC_PDP_012</t>
-  </si>
-  <si>
-    <t>Validate all the fields in the 'Review' tab are mandatory fields</t>
-  </si>
-  <si>
-    <t>TC_PDP_013</t>
-  </si>
-  <si>
-    <t>Validate 'Write a review' link under 'Add to Cart' button on the 'Product Display' page</t>
-  </si>
-  <si>
-    <t>TC_PDP_014</t>
-  </si>
-  <si>
-    <t>Validate average of the user reviews should be dispalyed under the 'Add to Cart' button of the Product Display page</t>
-  </si>
-  <si>
-    <t>TC_PDP_015</t>
-  </si>
-  <si>
-    <t>Validate the count of reviews should be displayed in the 'Reviews' tab label of the Product Display page</t>
-  </si>
-  <si>
-    <t>TC_PDP_016</t>
-  </si>
-  <si>
-    <t>Validate 'reviews' link under the 'Add to Cart' button of Product Display Page</t>
-  </si>
-  <si>
-    <t>TC_PDP_017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validate submitting a review without filling the mandatory fields </t>
-  </si>
-  <si>
-    <t>TC_PDP_018</t>
-  </si>
-  <si>
-    <t>Validate the review text given while writing is accepted according to the specified number of characters</t>
-  </si>
-  <si>
-    <t>TC_PDP_019</t>
-  </si>
-  <si>
-    <t>Validate adding the product to 'Wish List' from the Product Display page</t>
-  </si>
-  <si>
-    <t>TC_PDP_020</t>
-  </si>
-  <si>
-    <t>Validate adding the product for comparision from the Product Display page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the Application URL </t>
-  </si>
-  <si>
-    <t>TC_PDP_021</t>
-  </si>
-  <si>
-    <t>Validate proper options for liking, tweeting, sharing the Product Display page on social platforms</t>
-  </si>
-  <si>
-    <t>TC_PDP_022</t>
-  </si>
-  <si>
-    <t>Validate 'Related Products' section in Product Display page</t>
-  </si>
-  <si>
-    <t>TC_PDP_023</t>
-  </si>
-  <si>
-    <t>Validate navigating to the Product Display page by using the Product image in the 'Wish List' page</t>
-  </si>
-  <si>
-    <t>1. Open the Application URL and Login
-2.A product is added to the Wish List page</t>
-  </si>
-  <si>
-    <t>TC_PDP_024</t>
-  </si>
-  <si>
-    <t>Validate navigating to the Product Display page by using the Product Name link in the 'Wish List' page</t>
-  </si>
-  <si>
-    <t>TC_PDP_025</t>
-  </si>
-  <si>
-    <t>Validate navigating to the Product Display page by using the Product Name link in Success message on adding the Product to Cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the Application URL and Login
-</t>
-  </si>
-  <si>
-    <t>TC_PDP_026</t>
-  </si>
-  <si>
-    <t>Validate navigating to the Product Display page by using the Product Image in the 'Shopping Cart' page</t>
-  </si>
-  <si>
-    <t>TC_PDP_027</t>
-  </si>
-  <si>
-    <t>Validate navigating to the Product Display page by using the Product Name link in the 'Shopping Cart' page</t>
-  </si>
-  <si>
-    <t>TC_PDP_028</t>
-  </si>
-  <si>
-    <t>Validate navigating to the Product Display page by using the Product Name link in the 'Confirm Order' sectioon of the 'Checkout' page</t>
-  </si>
-  <si>
-    <t>TC_PDP_029</t>
-  </si>
-  <si>
-    <t>Validate navigating to the Product Display page by using the Product Image in the 'Cart' button toggle box</t>
-  </si>
-  <si>
-    <t>TC_PDP_030</t>
-  </si>
-  <si>
-    <t>Validate navigating to the Product Display page by using the Product Name link in the 'Cart' button toggle box</t>
-  </si>
-  <si>
-    <t>TC_PDP_031</t>
-  </si>
-  <si>
-    <t>Validate the Reward Points displayed in the Product Display page</t>
-  </si>
-  <si>
-    <t>TC_PDP_032</t>
-  </si>
-  <si>
-    <t>Validate the original price of the Product without offer in the Product Display page</t>
-  </si>
-  <si>
-    <t>TC_PDP_033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validate the prices of the Product when purchased in bulk </t>
-  </si>
-  <si>
-    <t>TC_PDP_034</t>
-  </si>
-  <si>
-    <t>Validate all the extra available options in the Product Display page</t>
-  </si>
-  <si>
-    <t>TC_PDP_035</t>
-  </si>
-  <si>
-    <t>Validate Page Title, Page Heading and Page URL of the 'Product Display' page</t>
-  </si>
-  <si>
-    <t>TC_PDP_036</t>
-  </si>
-  <si>
-    <t>Validate the UI of 'Product Display' page</t>
-  </si>
-  <si>
-    <t>TC_PDP_037</t>
-  </si>
-  <si>
-    <t>Validate the 'Product Display' page functionality in all the supported environments</t>
-  </si>
-  <si>
-    <t>TC_MA_001</t>
-  </si>
-  <si>
-    <t>(TS_013)
-My Account</t>
-  </si>
-  <si>
-    <t>Validate navigating to 'My Account' page from the 'Order Success' page</t>
-  </si>
-  <si>
-    <t>1. Open the Application URL, login and place an order for a product  - &lt;Refer Test Data&gt;</t>
-  </si>
-  <si>
-    <t>TC_MA_002</t>
-  </si>
-  <si>
-    <t>Validate navigating to 'My Account' page on login</t>
-  </si>
-  <si>
-    <t>TC_MA_003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validate navigating to 'My Account' page using 'My Account' option </t>
-  </si>
-  <si>
-    <t>TC_MA_004</t>
-  </si>
-  <si>
-    <t>Validate navigating to 'My Account' page using 'Right Column' options</t>
-  </si>
-  <si>
-    <t>TC_MA_005</t>
-  </si>
-  <si>
-    <t>Validate navigating to 'My Account' page using 'My Account' option in Site Map page</t>
-  </si>
-  <si>
-    <t>TC_MA_006</t>
-  </si>
-  <si>
-    <t>Validate Breadcrump in 'My Account' page</t>
-  </si>
-  <si>
-    <t>TC_MA_007</t>
-  </si>
-  <si>
-    <t>Validate Page URL, Page Heading and Page Title of the 'My Account' page</t>
-  </si>
-  <si>
-    <t>TC_MA_008</t>
-  </si>
-  <si>
-    <t>Validate the UI of 'My Account' page functionality</t>
-  </si>
-  <si>
-    <t>TC_MA_009</t>
-  </si>
-  <si>
-    <t>Validate the 'My Account' page functionality in all the supported environments</t>
-  </si>
-  <si>
-    <t>TC_CO_001</t>
-  </si>
-  <si>
-    <t>(TS_012)
-Checkout</t>
-  </si>
-  <si>
-    <t>Validate navigating to Checkout page when there are no products added to the Shopping Cart</t>
-  </si>
-  <si>
-    <t>1. Open the Application URL and ensure there are no products added to the Shopping Cart</t>
-  </si>
-  <si>
-    <t>TC_CO_002</t>
-  </si>
-  <si>
-    <t>Validate navigating to Checkout page from 'Shopping Cart' page</t>
-  </si>
-  <si>
-    <t>TC_CO_003</t>
-  </si>
-  <si>
-    <t>Validate navigating to Checkout page using 'Shopping Cart' header option</t>
-  </si>
-  <si>
-    <t>1. Open the Application URL and a product is added to Shopping Cart - &lt;Refer Test Data&gt;</t>
-  </si>
-  <si>
-    <t>TC_CO_004</t>
-  </si>
-  <si>
-    <t>Validate navigating to Checkout page using 'Checkout' option in the Cart block</t>
-  </si>
-  <si>
-    <t>TC_CO_005</t>
-  </si>
-  <si>
-    <t>Validate Checkout as SignedIn User ( SignIn Checkout ) by using an existing address during checkout</t>
-  </si>
-  <si>
-    <t>TC_CO_006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validate Checkout as SignedIn User ( SignIn Checkout ) by entering new address into the mandatory fields of the Billing Details section during checkout </t>
-  </si>
-  <si>
-    <t>TC_CO_007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validate Checkout as SignedIn User ( SignIn Checkout ) by entering new address into all the fields of the Billing Details section during checkout </t>
-  </si>
-  <si>
-    <t>TC_CO_008</t>
-  </si>
-  <si>
-    <t>Validate text fields in Billing Details of the Checkout page has Placeholders</t>
-  </si>
-  <si>
-    <t>TC_CO_009</t>
-  </si>
-  <si>
-    <t>Validate without entering any fields in the Billing Section of the Checkout Page</t>
-  </si>
-  <si>
-    <t>TC_CO_010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validate Checkout as SignedIn User ( SignIn Checkout ) by entering new address into the mandatory fields of the Delivery Details section during checkout </t>
-  </si>
-  <si>
-    <t>TC_CO_011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validate Checkout as SignedIn User ( SignIn Checkout ) by entering new address into all the fields of the Delivery Details section during checkout </t>
-  </si>
-  <si>
-    <t>TC_CO_012</t>
-  </si>
-  <si>
-    <t>Validate text fields in Delivery Details of the Checkout page has Placeholders</t>
-  </si>
-  <si>
-    <t>TC_CO_013</t>
-  </si>
-  <si>
-    <t>Validate without entering any fields in the Delivery Details Section of the Checkout Page</t>
-  </si>
-  <si>
-    <t>TC_CO_014</t>
-  </si>
-  <si>
-    <t>Validate adding comments about your order in the 'Delivery Method' section of Checkout page</t>
-  </si>
-  <si>
-    <t>TC_CO_015</t>
-  </si>
-  <si>
-    <t>Validate adding comments about your order in the 'Payment Method' section of Checkout page</t>
-  </si>
-  <si>
-    <t>TC_CO_016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validate Guest Checkout </t>
-  </si>
-  <si>
-    <t>1. Open the Application URL and don't login</t>
-  </si>
-  <si>
-    <t>TC_CO_017</t>
-  </si>
-  <si>
-    <t>Validate Checkout as New User</t>
-  </si>
-  <si>
-    <t>TC_CO_018</t>
-  </si>
-  <si>
-    <t>Checkout by SigningIn</t>
-  </si>
-  <si>
-    <t>TC_CO_019</t>
-  </si>
-  <si>
-    <t>Validate the UI of 'Checkout' functionality</t>
-  </si>
-  <si>
-    <t>TC_CO_020</t>
-  </si>
-  <si>
-    <t>Validate the 'Checkout' functionality in all the supported environments</t>
-  </si>
-  <si>
-    <t>Project Name (Client Name)</t>
-  </si>
-  <si>
-    <t>Prepared By</t>
-  </si>
-  <si>
-    <t>Yusha</t>
-  </si>
-  <si>
-    <t>Mansib</t>
-  </si>
-  <si>
-    <t>Plush toys</t>
-  </si>
-  <si>
-    <t>1. Product should be successfully displayed in the 'My Wish List' page</t>
   </si>
   <si>
     <t xml:space="preserve">1. Enter any existing Product name into the Search text box field - &lt;Refer Test Data&gt;
@@ -937,6 +461,18 @@
 </t>
   </si>
   <si>
+    <t>Plush toys</t>
+  </si>
+  <si>
+    <t>1. Product should be successfully displayed in the 'My Wish List' page</t>
+  </si>
+  <si>
+    <t>TC_WL_003</t>
+  </si>
+  <si>
+    <t>Validate adding a product to 'Wish List' page from the Product that is displayed in the 'Featured' section of 'Home' page</t>
+  </si>
+  <si>
     <t xml:space="preserve">1. Scroll down till the 'Our Latest Products' section on the Home page is displayed 
 2. Click on 'Add to Wish List heart Icon' option on a product that is displayed 
 </t>
@@ -947,9 +483,29 @@
 3. Product should be successfully displayed in the 'My Wish List' page</t>
   </si>
   <si>
+    <t>TC_WL_004</t>
+  </si>
+  <si>
+    <t>Validate adding the product to Wish List from the Products displayed in the category or sub-category page</t>
+  </si>
+  <si>
+    <t>1. Open the Application URL and login</t>
+  </si>
+  <si>
     <t>1. Scroll down till the 'Product Categories' section on the Home page is displayed. 
 2. Click on any categories that is displayed. 
 3.Click on 'Add to Wish List heart Icon' option on a product that is displayed</t>
+  </si>
+  <si>
+    <t>1.User should be taken to Category page.
+2. Add to wishlist Heart Icon color changed to red as marked
+3. Product should be successfully displayed in the 'My Wish List' page</t>
+  </si>
+  <si>
+    <t>TC_WL_005</t>
+  </si>
+  <si>
+    <t>Validate navigating to 'My Wish List' page using the 'Wish List' header option</t>
   </si>
   <si>
     <t xml:space="preserve">1. Enter any existing Product name into the Search text box field / Click any product from all products
@@ -958,6 +514,15 @@
 </t>
   </si>
   <si>
+    <t>1. User should be taken to Product page.
+2. Add to wishlist Heart Icon color changed to red as marked
+3. By clicking the heart icon on top right nave redirect to wishlist page.
+4. Product should be successfully displayed in the 'My Wish List' page</t>
+  </si>
+  <si>
+    <t>TC_WL_006</t>
+  </si>
+  <si>
     <t>Validate navigating to 'My Wish List' page using the 'Left Column' menu options</t>
   </si>
   <si>
@@ -965,6 +530,19 @@
 2. Click on 'Add to Wish List' option on a product that is displayed 
 3. Click on the 'Menu Option' displayed top left Under Logo
 4.Click 'My wishlist</t>
+  </si>
+  <si>
+    <t>1.User should be taken to Product page.
+2. Add to wishlist Heart Icon color changed to red as marked
+3. By clicking the Menu on top left nav Display sidebar options
+4.By Clicking 'My wishlist navigates to wishlist page
+5. Product should be successfully displayed in the 'My Wish List' page</t>
+  </si>
+  <si>
+    <t>TC_WL_007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate navigating to 'My Wish List' page from the 'My Account' page </t>
   </si>
   <si>
     <t>1. Enter any existing Product name into the Search text box field / Click any product from all products
@@ -983,19 +561,89 @@
 7. Product should be successfully displayed in the 'My Wish List' page.</t>
   </si>
   <si>
-    <t>1. Proper UI adhering to the UI checklist should be displayed for the 'Wish List' functionality</t>
-  </si>
-  <si>
-    <t>Validate the 'Wish List' functionality in all the supported environments</t>
-  </si>
-  <si>
-    <t>1. Check the 'Wish List' functionality in all the supported environments</t>
-  </si>
-  <si>
-    <t>1. Check the UI of the functioanality related to 'Wish List'</t>
-  </si>
-  <si>
-    <t>1. 'Wish List' functionality should work correctly in all the supported environments</t>
+    <t>TC_WL_008</t>
+  </si>
+  <si>
+    <t>Validate the 'My Wish List' page when there are no products added</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click on 'Add to Wish List' page on top right nav that is displayed 
+</t>
+  </si>
+  <si>
+    <t>1. User should be taken to wishlist page displayed  message 'No wishlist is available!' with sad emoji</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>TC_WL_009</t>
+  </si>
+  <si>
+    <t>Validate the 'My Wish List' page when only one product is added to it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter any existing Product name into the Search text box field / Click any product from all products
+2. Click on 'Add to Wish List' option on a product that is displayed 
+3. Click on the 'wish list! Heart' Icon displayed top right beside cart icon
+4. Navigate to My wish list page
+</t>
+  </si>
+  <si>
+    <t>1. User should be taken to Product page.
+2. Add to wishlist Heart Icon color changed to red as marked
+3. By clicking the heart icon on top right nave redirect to wishlist page.
+4. Only a Single Product should be successfully displayed in the 'My Wish List' page</t>
+  </si>
+  <si>
+    <t>TC_WL_010</t>
+  </si>
+  <si>
+    <t>Validate the removing the Product  from 'My Wish List' page</t>
+  </si>
+  <si>
+    <t>1. Enter any existing Product name into the Search text box field / Click any product from all products
+2. Click on 'Add to Wish List' option on a product that is displayed 
+3. Click on the 'wish list! Heart' Icon displayed top right beside cart icon
+4. Navigate to My wish list page
+5. CLick the heart icon displayed on product</t>
+  </si>
+  <si>
+    <t>1. User should be taken to Product page.
+2. Add to wishlist Heart Icon color changed to red as marked
+3. By clicking the heart icon on top right nav redirect to wishlist page.
+4. Product should be successfully displayed in the 'My Wish List' page
+5. By clicking the icon will remove the product from the page</t>
+  </si>
+  <si>
+    <t>TC_WL_011</t>
+  </si>
+  <si>
+    <t>Validate adding the multiple products to the 'My Wish List' page</t>
+  </si>
+  <si>
+    <t>1. Open the Application URL and login
+2. One product is added to 'My Wish List' page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter any existing Product name into the Search text box field / Click any product from all products
+2. Click on 'Add to Wish List' option on a product that is displayed
+3. Repeat step 2 for multiple times
+4. Click on the 'wish list! Heart' Icon displayed top right beside cart icon
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.User should be taken to Product page.
+2. Add to wishlist Heart Icon color changed to red as marked
+3. By clicking the heart icon on top right nav redirect to wishlist page.
+4. Multiple Product should be successfully displayed in the 'My Wish List' page
+</t>
+  </si>
+  <si>
+    <t>TC_WL_012</t>
+  </si>
+  <si>
+    <t>Validate adding duplicate products to 'My Wish List' page</t>
   </si>
   <si>
     <t xml:space="preserve">1. Enter any existing Product name into the Search text box field / Click any product from all products
@@ -1012,76 +660,42 @@
 .</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click on 'Add to Wish List' page on top right nav that is displayed 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>1. User should be taken to wishlist page displayed  message 'No wishlist is available!' with sad emoji</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enter any existing Product name into the Search text box field / Click any product from all products
-2. Click on 'Add to Wish List' option on a product that is displayed 
-3. Click on the 'wish list! Heart' Icon displayed top right beside cart icon
-4. Navigate to My wish list page
-</t>
-  </si>
-  <si>
-    <t>1. Enter any existing Product name into the Search text box field / Click any product from all products
-2. Click on 'Add to Wish List' option on a product that is displayed 
-3. Click on the 'wish list! Heart' Icon displayed top right beside cart icon
-4. Navigate to My wish list page
-5. CLick the heart icon displayed on product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enter any existing Product name into the Search text box field / Click any product from all products
-2. Click on 'Add to Wish List' option on a product that is displayed
-3. Repeat step 2 for multiple times
-4. Click on the 'wish list! Heart' Icon displayed top right beside cart icon
-</t>
+    <t>TC_WL_013</t>
+  </si>
+  <si>
+    <t>Validate the UI of 'Wish List' funtionality</t>
+  </si>
+  <si>
+    <t>1. Open the Application URL and login
+2. Add multiple products to 'My Wish List' page</t>
+  </si>
+  <si>
+    <t>1. Check the UI of the functioanality related to 'Wish List'</t>
+  </si>
+  <si>
+    <t>1. Proper UI adhering to the UI checklist should be displayed for the 'Wish List' functionality</t>
+  </si>
+  <si>
+    <t>TC_WL_014</t>
+  </si>
+  <si>
+    <t>Validate the 'Wish List' functionality in all the supported environments</t>
+  </si>
+  <si>
+    <t>1. Check the 'Wish List' functionality in all the supported environments</t>
+  </si>
+  <si>
+    <t>1. 'Wish List' functionality should work correctly in all the supported environments</t>
+  </si>
+  <si>
+    <t>TC_PDP_001</t>
+  </si>
+  <si>
+    <t>(TS_007)
+Product Display Page</t>
   </si>
   <si>
     <t xml:space="preserve">Validate the Thumbnails of the Product displayed in the Product Display Page
-</t>
-  </si>
-  <si>
-    <t>1.User should be taken to Category page.
-2. Add to wishlist Heart Icon color changed to red as marked
-3. Product should be successfully displayed in the 'My Wish List' page</t>
-  </si>
-  <si>
-    <t>1. User should be taken to Product page.
-2. Add to wishlist Heart Icon color changed to red as marked
-3. By clicking the heart icon on top right nave redirect to wishlist page.
-4. Product should be successfully displayed in the 'My Wish List' page</t>
-  </si>
-  <si>
-    <t>1.User should be taken to Product page.
-2. Add to wishlist Heart Icon color changed to red as marked
-3. By clicking the Menu on top left nav Display sidebar options
-4.By Clicking 'My wishlist navigates to wishlist page
-5. Product should be successfully displayed in the 'My Wish List' page</t>
-  </si>
-  <si>
-    <t>1. User should be taken to Product page.
-2. Add to wishlist Heart Icon color changed to red as marked
-3. By clicking the heart icon on top right nave redirect to wishlist page.
-4. Only a Single Product should be successfully displayed in the 'My Wish List' page</t>
-  </si>
-  <si>
-    <t>1. User should be taken to Product page.
-2. Add to wishlist Heart Icon color changed to red as marked
-3. By clicking the heart icon on top right nav redirect to wishlist page.
-4. Product should be successfully displayed in the 'My Wish List' page
-5. By clicking the icon will remove the product from the page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.User should be taken to Product page.
-2. Add to wishlist Heart Icon color changed to red as marked
-3. By clicking the heart icon on top right nav redirect to wishlist page.
-4. Multiple Product should be successfully displayed in the 'My Wish List' page
 </t>
   </si>
   <si>
@@ -1092,13 +706,437 @@
   <si>
     <t>1. User should be taken to Home page.
 2. Product should be successfully displayed in the section.</t>
+  </si>
+  <si>
+    <t>TC_PDP_002</t>
+  </si>
+  <si>
+    <t>Validate that Product Name, Brand and Product Code are displayed in the Product Display Page</t>
+  </si>
+  <si>
+    <t>TC_PDP_003</t>
+  </si>
+  <si>
+    <t>Validate the availabilty status of the Product in the Product Display Page</t>
+  </si>
+  <si>
+    <t>TC_PDP_004</t>
+  </si>
+  <si>
+    <t>Validate the Price of the Product with and without tax is displayed in the Product Display Page</t>
+  </si>
+  <si>
+    <t>TC_PDP_005</t>
+  </si>
+  <si>
+    <t>Validate the default quanity for the Product is displayed as 1 in the Product Display Page, when there is no minimum quantity set for the Product</t>
+  </si>
+  <si>
+    <t>TC_PDP_006</t>
+  </si>
+  <si>
+    <t>Validate the negative quantity or zero quantity or null quantity should not be allowed in the Product Display Page</t>
+  </si>
+  <si>
+    <t>TC_PDP_007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate the Product having the minimum quanitity set </t>
+  </si>
+  <si>
+    <t>TC_PDP_008</t>
+  </si>
+  <si>
+    <t>Validate the description of the Product in the Product Display Page</t>
+  </si>
+  <si>
+    <t>TC_PDP_009</t>
+  </si>
+  <si>
+    <t>Validate the specifications of the Product in the Product Display Page</t>
+  </si>
+  <si>
+    <t>TC_PDP_010</t>
+  </si>
+  <si>
+    <t>Validate the User is able to write a review for the Product from the 'Reviews' tab of Product Display Page</t>
+  </si>
+  <si>
+    <t>TC_PDP_011</t>
+  </si>
+  <si>
+    <t>Validate the 'Reviews' tab when there are no reviews or zero reviews added</t>
+  </si>
+  <si>
+    <t>TC_PDP_012</t>
+  </si>
+  <si>
+    <t>Validate all the fields in the 'Review' tab are mandatory fields</t>
+  </si>
+  <si>
+    <t>TC_PDP_013</t>
+  </si>
+  <si>
+    <t>Validate 'Write a review' link under 'Add to Cart' button on the 'Product Display' page</t>
+  </si>
+  <si>
+    <t>TC_PDP_014</t>
+  </si>
+  <si>
+    <t>Validate average of the user reviews should be dispalyed under the 'Add to Cart' button of the Product Display page</t>
+  </si>
+  <si>
+    <t>TC_PDP_015</t>
+  </si>
+  <si>
+    <t>Validate the count of reviews should be displayed in the 'Reviews' tab label of the Product Display page</t>
+  </si>
+  <si>
+    <t>TC_PDP_016</t>
+  </si>
+  <si>
+    <t>Validate 'reviews' link under the 'Add to Cart' button of Product Display Page</t>
+  </si>
+  <si>
+    <t>TC_PDP_017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate submitting a review without filling the mandatory fields </t>
+  </si>
+  <si>
+    <t>TC_PDP_018</t>
+  </si>
+  <si>
+    <t>Validate the review text given while writing is accepted according to the specified number of characters</t>
+  </si>
+  <si>
+    <t>TC_PDP_019</t>
+  </si>
+  <si>
+    <t>Validate adding the product to 'Wish List' from the Product Display page</t>
+  </si>
+  <si>
+    <t>TC_PDP_020</t>
+  </si>
+  <si>
+    <t>Validate adding the product for comparision from the Product Display page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the Application URL </t>
+  </si>
+  <si>
+    <t>TC_PDP_021</t>
+  </si>
+  <si>
+    <t>Validate proper options for liking, tweeting, sharing the Product Display page on social platforms</t>
+  </si>
+  <si>
+    <t>TC_PDP_022</t>
+  </si>
+  <si>
+    <t>Validate 'Related Products' section in Product Display page</t>
+  </si>
+  <si>
+    <t>TC_PDP_023</t>
+  </si>
+  <si>
+    <t>Validate navigating to the Product Display page by using the Product image in the 'Wish List' page</t>
+  </si>
+  <si>
+    <t>1. Open the Application URL and Login
+2.A product is added to the Wish List page</t>
+  </si>
+  <si>
+    <t>TC_PDP_024</t>
+  </si>
+  <si>
+    <t>Validate navigating to the Product Display page by using the Product Name link in the 'Wish List' page</t>
+  </si>
+  <si>
+    <t>TC_PDP_025</t>
+  </si>
+  <si>
+    <t>Validate navigating to the Product Display page by using the Product Name link in Success message on adding the Product to Cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the Application URL and Login
+</t>
+  </si>
+  <si>
+    <t>TC_PDP_026</t>
+  </si>
+  <si>
+    <t>Validate navigating to the Product Display page by using the Product Image in the 'Shopping Cart' page</t>
+  </si>
+  <si>
+    <t>TC_PDP_027</t>
+  </si>
+  <si>
+    <t>Validate navigating to the Product Display page by using the Product Name link in the 'Shopping Cart' page</t>
+  </si>
+  <si>
+    <t>TC_PDP_028</t>
+  </si>
+  <si>
+    <t>Validate navigating to the Product Display page by using the Product Name link in the 'Confirm Order' sectioon of the 'Checkout' page</t>
+  </si>
+  <si>
+    <t>TC_PDP_029</t>
+  </si>
+  <si>
+    <t>Validate navigating to the Product Display page by using the Product Image in the 'Cart' button toggle box</t>
+  </si>
+  <si>
+    <t>TC_PDP_030</t>
+  </si>
+  <si>
+    <t>Validate navigating to the Product Display page by using the Product Name link in the 'Cart' button toggle box</t>
+  </si>
+  <si>
+    <t>TC_PDP_031</t>
+  </si>
+  <si>
+    <t>Validate the Reward Points displayed in the Product Display page</t>
+  </si>
+  <si>
+    <t>TC_PDP_032</t>
+  </si>
+  <si>
+    <t>Validate the original price of the Product without offer in the Product Display page</t>
+  </si>
+  <si>
+    <t>TC_PDP_033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate the prices of the Product when purchased in bulk </t>
+  </si>
+  <si>
+    <t>TC_PDP_034</t>
+  </si>
+  <si>
+    <t>Validate all the extra available options in the Product Display page</t>
+  </si>
+  <si>
+    <t>TC_PDP_035</t>
+  </si>
+  <si>
+    <t>Validate Page Title, Page Heading and Page URL of the 'Product Display' page</t>
+  </si>
+  <si>
+    <t>TC_PDP_036</t>
+  </si>
+  <si>
+    <t>Validate the UI of 'Product Display' page</t>
+  </si>
+  <si>
+    <t>TC_PDP_037</t>
+  </si>
+  <si>
+    <t>Validate the 'Product Display' page functionality in all the supported environments</t>
+  </si>
+  <si>
+    <t>&lt;&lt; Test Scenarios</t>
+  </si>
+  <si>
+    <t>TC_CO_001</t>
+  </si>
+  <si>
+    <t>(TS_012)
+Checkout</t>
+  </si>
+  <si>
+    <t>Validate navigating to Checkout page when there are no products added to the Shopping Cart</t>
+  </si>
+  <si>
+    <t>1. Open the Application URL and ensure there are no products added to the Shopping Cart</t>
+  </si>
+  <si>
+    <t>TC_CO_002</t>
+  </si>
+  <si>
+    <t>Validate navigating to Checkout page from 'Shopping Cart' page</t>
+  </si>
+  <si>
+    <t>TC_CO_003</t>
+  </si>
+  <si>
+    <t>Validate navigating to Checkout page using 'Shopping Cart' header option</t>
+  </si>
+  <si>
+    <t>1. Open the Application URL and a product is added to Shopping Cart - &lt;Refer Test Data&gt;</t>
+  </si>
+  <si>
+    <t>TC_CO_004</t>
+  </si>
+  <si>
+    <t>Validate navigating to Checkout page using 'Checkout' option in the Cart block</t>
+  </si>
+  <si>
+    <t>TC_CO_005</t>
+  </si>
+  <si>
+    <t>Validate Checkout as SignedIn User ( SignIn Checkout ) by using an existing address during checkout</t>
+  </si>
+  <si>
+    <t>TC_CO_006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate Checkout as SignedIn User ( SignIn Checkout ) by entering new address into the mandatory fields of the Billing Details section during checkout </t>
+  </si>
+  <si>
+    <t>TC_CO_007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate Checkout as SignedIn User ( SignIn Checkout ) by entering new address into all the fields of the Billing Details section during checkout </t>
+  </si>
+  <si>
+    <t>TC_CO_008</t>
+  </si>
+  <si>
+    <t>Validate text fields in Billing Details of the Checkout page has Placeholders</t>
+  </si>
+  <si>
+    <t>TC_CO_009</t>
+  </si>
+  <si>
+    <t>Validate without entering any fields in the Billing Section of the Checkout Page</t>
+  </si>
+  <si>
+    <t>TC_CO_010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate Checkout as SignedIn User ( SignIn Checkout ) by entering new address into the mandatory fields of the Delivery Details section during checkout </t>
+  </si>
+  <si>
+    <t>TC_CO_011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate Checkout as SignedIn User ( SignIn Checkout ) by entering new address into all the fields of the Delivery Details section during checkout </t>
+  </si>
+  <si>
+    <t>TC_CO_012</t>
+  </si>
+  <si>
+    <t>Validate text fields in Delivery Details of the Checkout page has Placeholders</t>
+  </si>
+  <si>
+    <t>TC_CO_013</t>
+  </si>
+  <si>
+    <t>Validate without entering any fields in the Delivery Details Section of the Checkout Page</t>
+  </si>
+  <si>
+    <t>TC_CO_014</t>
+  </si>
+  <si>
+    <t>Validate adding comments about your order in the 'Delivery Method' section of Checkout page</t>
+  </si>
+  <si>
+    <t>TC_CO_015</t>
+  </si>
+  <si>
+    <t>Validate adding comments about your order in the 'Payment Method' section of Checkout page</t>
+  </si>
+  <si>
+    <t>TC_CO_016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate Guest Checkout </t>
+  </si>
+  <si>
+    <t>1. Open the Application URL and don't login</t>
+  </si>
+  <si>
+    <t>TC_CO_017</t>
+  </si>
+  <si>
+    <t>Validate Checkout as New User</t>
+  </si>
+  <si>
+    <t>TC_CO_018</t>
+  </si>
+  <si>
+    <t>Checkout by SigningIn</t>
+  </si>
+  <si>
+    <t>TC_CO_019</t>
+  </si>
+  <si>
+    <t>Validate the UI of 'Checkout' functionality</t>
+  </si>
+  <si>
+    <t>TC_CO_020</t>
+  </si>
+  <si>
+    <t>Validate the 'Checkout' functionality in all the supported environments</t>
+  </si>
+  <si>
+    <t>TC_MA_001</t>
+  </si>
+  <si>
+    <t>(TS_013)
+My Account</t>
+  </si>
+  <si>
+    <t>Validate navigating to 'My Account' page from the 'Order Success' page</t>
+  </si>
+  <si>
+    <t>1. Open the Application URL, login and place an order for a product  - &lt;Refer Test Data&gt;</t>
+  </si>
+  <si>
+    <t>TC_MA_002</t>
+  </si>
+  <si>
+    <t>Validate navigating to 'My Account' page on login</t>
+  </si>
+  <si>
+    <t>TC_MA_003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate navigating to 'My Account' page using 'My Account' option </t>
+  </si>
+  <si>
+    <t>TC_MA_004</t>
+  </si>
+  <si>
+    <t>Validate navigating to 'My Account' page using 'Right Column' options</t>
+  </si>
+  <si>
+    <t>TC_MA_005</t>
+  </si>
+  <si>
+    <t>Validate navigating to 'My Account' page using 'My Account' option in Site Map page</t>
+  </si>
+  <si>
+    <t>TC_MA_006</t>
+  </si>
+  <si>
+    <t>Validate Breadcrump in 'My Account' page</t>
+  </si>
+  <si>
+    <t>TC_MA_007</t>
+  </si>
+  <si>
+    <t>Validate Page URL, Page Heading and Page Title of the 'My Account' page</t>
+  </si>
+  <si>
+    <t>TC_MA_008</t>
+  </si>
+  <si>
+    <t>Validate the UI of 'My Account' page functionality</t>
+  </si>
+  <si>
+    <t>TC_MA_009</t>
+  </si>
+  <si>
+    <t>Validate the 'My Account' page functionality in all the supported environments</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1371,7 +1409,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1447,15 +1485,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1464,68 +1493,20 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1543,6 +1524,19 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Test Scenarios"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1843,55 +1837,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38BB553C-C88C-4950-A156-B9B887AE9146}">
   <dimension ref="C5:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="50.5546875" customWidth="1"/>
-    <col min="4" max="4" width="35.6640625" customWidth="1"/>
-    <col min="5" max="5" width="66.44140625" customWidth="1"/>
+    <col min="3" max="3" width="50.5703125" customWidth="1"/>
+    <col min="4" max="4" width="35.7109375" customWidth="1"/>
+    <col min="5" max="5" width="66.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="C5" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="D5" s="31" t="s">
-        <v>271</v>
-      </c>
-      <c r="E5" s="32"/>
-    </row>
-    <row r="6" spans="3:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="C6" s="33" t="s">
-        <v>270</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="E6" s="32"/>
-    </row>
-    <row r="7" spans="3:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="C7" s="28"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-    </row>
-    <row r="8" spans="3:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="C8" s="29"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-    </row>
-    <row r="9" spans="3:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="C9" s="29"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-    </row>
-    <row r="10" spans="3:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="C10" s="29"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-    </row>
-    <row r="11" spans="3:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:5" ht="18">
+      <c r="C5" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="29"/>
+    </row>
+    <row r="6" spans="3:5" ht="18">
+      <c r="C6" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="29"/>
+    </row>
+    <row r="7" spans="3:5" ht="18">
+      <c r="C7" s="34"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+    </row>
+    <row r="8" spans="3:5" ht="18">
+      <c r="C8" s="35"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+    </row>
+    <row r="9" spans="3:5" ht="18">
+      <c r="C9" s="35"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+    </row>
+    <row r="10" spans="3:5" ht="18">
+      <c r="C10" s="35"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+    </row>
+    <row r="11" spans="3:5" ht="18">
       <c r="C11" s="36"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1904,137 +1898,137 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C53E4CD7-4770-4717-8FD4-1AFB2D24EBE2}">
   <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.109375" customWidth="1"/>
-    <col min="2" max="3" width="18.77734375" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" customWidth="1"/>
-    <col min="5" max="5" width="18.77734375" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="8" width="16.88671875" customWidth="1"/>
-    <col min="9" max="9" width="11.77734375" customWidth="1"/>
-    <col min="10" max="10" width="11.21875" customWidth="1"/>
-    <col min="11" max="11" width="12.109375" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="2" max="3" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="23.7109375" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="128.25">
+      <c r="A2" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="114" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>27</v>
-      </c>
       <c r="C2" s="13" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" s="12"/>
       <c r="J2" s="14"/>
       <c r="K2" s="15"/>
     </row>
-    <row r="3" spans="1:11" ht="91.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="90">
       <c r="A3" s="12" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="13" t="s">
+      <c r="G3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="18" t="s">
         <v>22</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>21</v>
       </c>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
       <c r="K3" s="17"/>
     </row>
-    <row r="4" spans="1:11" ht="91.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="90">
       <c r="A4" s="12" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D4" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="18" t="s">
         <v>22</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>21</v>
       </c>
       <c r="I4" s="12"/>
       <c r="J4" s="14"/>
@@ -2049,136 +2043,136 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE25C0BD-2C08-4426-8A88-212753609618}">
   <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.44140625" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" customWidth="1"/>
-    <col min="4" max="4" width="25.21875" customWidth="1"/>
+    <col min="1" max="1" width="21.42578125" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="15.21875" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" customWidth="1"/>
-    <col min="11" max="11" width="8.88671875" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="11" max="11" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" s="5" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="57" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="56.25">
       <c r="A2" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="G2" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" s="12"/>
       <c r="J2" s="14"/>
       <c r="K2" s="15"/>
     </row>
-    <row r="3" spans="1:11" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="45">
       <c r="A3" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" s="12"/>
       <c r="J3" s="14"/>
       <c r="K3" s="15"/>
     </row>
-    <row r="4" spans="1:11" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="56.25">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" s="12"/>
       <c r="J4" s="14"/>
@@ -2191,225 +2185,263 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{613FE520-D496-4FE5-966F-6D1F22709934}">
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" customWidth="1"/>
-    <col min="3" max="3" width="27.44140625" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="5" max="5" width="30.33203125" customWidth="1"/>
-    <col min="6" max="6" width="18.44140625" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" customWidth="1"/>
-    <col min="11" max="11" width="13.44140625" customWidth="1"/>
+    <col min="5" max="5" width="30.28515625" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" customWidth="1"/>
+    <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" s="11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="50.25">
       <c r="A2" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>21</v>
+        <v>50</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="10"/>
       <c r="K2" s="9"/>
     </row>
-    <row r="3" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="176.25">
       <c r="A3" s="6" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="9"/>
+        <v>54</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>22</v>
+      </c>
       <c r="I3" s="9"/>
       <c r="J3" s="10"/>
       <c r="K3" s="9"/>
     </row>
-    <row r="4" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="100.5">
       <c r="A4" s="6" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="9"/>
+        <v>58</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>22</v>
+      </c>
       <c r="I4" s="9"/>
       <c r="J4" s="10"/>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="163.5">
       <c r="A5" s="6" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="9"/>
+        <v>62</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>22</v>
+      </c>
       <c r="I5" s="9"/>
       <c r="J5" s="10"/>
       <c r="K5" s="9"/>
     </row>
-    <row r="6" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="63">
       <c r="A6" s="6" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="9"/>
+        <v>66</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>22</v>
+      </c>
       <c r="I6" s="9"/>
       <c r="J6" s="10"/>
       <c r="K6" s="9"/>
     </row>
-    <row r="7" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="88.5">
       <c r="A7" s="6" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="9"/>
+        <v>71</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>22</v>
+      </c>
       <c r="I7" s="9"/>
       <c r="J7" s="10"/>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="75.75">
       <c r="A8" s="6" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>22</v>
+      </c>
       <c r="I8" s="9"/>
       <c r="J8" s="10"/>
       <c r="K8" s="9"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11">
       <c r="A9" s="6" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="8"/>
@@ -2417,14 +2449,14 @@
       <c r="E9" s="8"/>
       <c r="F9" s="7"/>
       <c r="G9" s="8"/>
-      <c r="H9" s="9"/>
+      <c r="H9" s="14"/>
       <c r="I9" s="9"/>
       <c r="J9" s="10"/>
       <c r="K9" s="9"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11">
       <c r="A10" s="6" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="8"/>
@@ -2432,14 +2464,14 @@
       <c r="E10" s="8"/>
       <c r="F10" s="7"/>
       <c r="G10" s="8"/>
-      <c r="H10" s="9"/>
+      <c r="H10" s="14"/>
       <c r="I10" s="9"/>
       <c r="J10" s="10"/>
       <c r="K10" s="9"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11">
       <c r="A11" s="6" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="8"/>
@@ -2447,10 +2479,16 @@
       <c r="E11" s="8"/>
       <c r="F11" s="7"/>
       <c r="G11" s="8"/>
-      <c r="H11" s="9"/>
+      <c r="H11" s="14"/>
       <c r="I11" s="9"/>
       <c r="J11" s="10"/>
       <c r="K11" s="9"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="H12" s="14"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="H13" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2461,217 +2499,229 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A880648-65F7-4FB7-8B6A-B3F299F6F34C}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
-    <col min="3" max="3" width="36.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="36.42578125" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="37.21875" customWidth="1"/>
-    <col min="6" max="6" width="24.5546875" customWidth="1"/>
-    <col min="7" max="7" width="26.44140625" customWidth="1"/>
-    <col min="8" max="8" width="15.21875" customWidth="1"/>
+    <col min="5" max="5" width="37.28515625" customWidth="1"/>
+    <col min="6" max="6" width="24.5703125" customWidth="1"/>
+    <col min="7" max="7" width="26.42578125" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" s="20" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H1" s="20" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I1" s="20" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="152.25">
       <c r="A2" s="22" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="D2" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="23" t="s">
-        <v>82</v>
-      </c>
       <c r="F2" s="23" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="H2" s="22"/>
+        <v>86</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>22</v>
+      </c>
       <c r="I2" s="22"/>
       <c r="J2" s="21"/>
       <c r="K2" s="22"/>
     </row>
-    <row r="3" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="121.5">
       <c r="A3" s="22" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="E3" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="23" t="s">
-        <v>81</v>
-      </c>
       <c r="G3" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="H3" s="22"/>
+        <v>91</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>22</v>
+      </c>
       <c r="I3" s="22"/>
       <c r="J3" s="21"/>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="121.5">
       <c r="A4" s="22" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C4" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>96</v>
-      </c>
       <c r="F4" s="23" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="H4" s="22"/>
+        <v>91</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>22</v>
+      </c>
       <c r="I4" s="22"/>
       <c r="J4" s="21"/>
       <c r="K4" s="22"/>
     </row>
-    <row r="5" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="121.5">
       <c r="A5" s="22" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E5" s="24" t="s">
         <v>97</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="H5" s="22"/>
+        <v>91</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>22</v>
+      </c>
       <c r="I5" s="22"/>
       <c r="J5" s="21"/>
       <c r="K5" s="22"/>
     </row>
-    <row r="6" spans="1:11" ht="69" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="53.25">
       <c r="A6" s="22" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="H6" s="22"/>
+        <v>102</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>22</v>
+      </c>
       <c r="I6" s="22"/>
       <c r="J6" s="21"/>
       <c r="K6" s="22"/>
     </row>
-    <row r="7" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="40.5">
       <c r="A7" s="22" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="H7" s="22"/>
+        <v>106</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>22</v>
+      </c>
       <c r="I7" s="22"/>
       <c r="J7" s="21"/>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11">
       <c r="A8" s="22"/>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
@@ -2684,7 +2734,7 @@
       <c r="J8" s="21"/>
       <c r="K8" s="22"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11">
       <c r="A9" s="22"/>
       <c r="B9" s="23"/>
       <c r="C9" s="23"/>
@@ -2697,7 +2747,7 @@
       <c r="J9" s="21"/>
       <c r="K9" s="22"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11">
       <c r="A10" s="22"/>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
@@ -2719,419 +2769,419 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19EDBD37-3B8C-49BB-8B11-BBBA72D23E70}">
   <dimension ref="A1:K20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="23.109375" customWidth="1"/>
-    <col min="4" max="4" width="24.44140625" customWidth="1"/>
-    <col min="5" max="5" width="25.77734375" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" customWidth="1"/>
-    <col min="7" max="7" width="25.88671875" customWidth="1"/>
-    <col min="8" max="8" width="16.88671875" customWidth="1"/>
-    <col min="11" max="11" width="23.5546875" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" customWidth="1"/>
+    <col min="4" max="4" width="24.42578125" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" customWidth="1"/>
+    <col min="11" max="11" width="23.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" s="11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="163.80000000000001" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="165.75">
       <c r="A2" s="6" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>110</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" s="37" t="s">
-        <v>275</v>
+        <v>111</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>112</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="G2" s="38" t="s">
-        <v>274</v>
+        <v>113</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="J2" s="10"/>
       <c r="K2" s="9"/>
     </row>
-    <row r="3" spans="1:11" ht="113.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="114.75">
       <c r="A3" s="6" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="D3" s="8"/>
-      <c r="E3" s="39" t="s">
-        <v>276</v>
-      </c>
-      <c r="F3" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="42" t="s">
-        <v>277</v>
+      <c r="E3" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>118</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
       <c r="J3" s="10"/>
       <c r="K3" s="9"/>
     </row>
-    <row r="4" spans="1:11" ht="138.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="140.25">
       <c r="A4" s="6" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E4" s="42" t="s">
-        <v>278</v>
-      </c>
-      <c r="F4" s="41" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="42" t="s">
-        <v>298</v>
+        <v>121</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
       <c r="J4" s="10"/>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:11" ht="151.19999999999999" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="153">
       <c r="A5" s="6" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>111</v>
+        <v>109</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>125</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E5" s="44" t="s">
-        <v>279</v>
+        <v>121</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>126</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="G5" s="44" t="s">
-        <v>299</v>
+        <v>113</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>127</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
       <c r="J5" s="10"/>
       <c r="K5" s="9"/>
     </row>
-    <row r="6" spans="1:11" ht="176.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="178.5">
       <c r="A6" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" s="42" t="s">
-        <v>280</v>
-      </c>
-      <c r="D6" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="E6" s="44" t="s">
-        <v>281</v>
-      </c>
-      <c r="F6" s="43" t="s">
-        <v>273</v>
-      </c>
-      <c r="G6" s="44" t="s">
-        <v>300</v>
+      <c r="C6" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>131</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
       <c r="J6" s="10"/>
       <c r="K6" s="9"/>
     </row>
-    <row r="7" spans="1:11" ht="226.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="216.75">
       <c r="A7" s="6" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="D7" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="E7" s="44" t="s">
-        <v>282</v>
-      </c>
-      <c r="F7" s="43" t="s">
-        <v>273</v>
-      </c>
-      <c r="G7" s="44" t="s">
-        <v>283</v>
+        <v>109</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>135</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="J7" s="10"/>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="63.75">
       <c r="A8" s="6" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="52" t="s">
-        <v>119</v>
-      </c>
-      <c r="D8" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="E8" s="52" t="s">
-        <v>291</v>
+        <v>109</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>138</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="H8" s="54" t="s">
-        <v>292</v>
+        <v>139</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="10"/>
       <c r="K8" s="9"/>
     </row>
-    <row r="9" spans="1:11" ht="176.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="178.5">
       <c r="A9" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="52" t="s">
-        <v>121</v>
-      </c>
-      <c r="D9" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="E9" s="54" t="s">
-        <v>294</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="G9" s="54" t="s">
-        <v>301</v>
+      <c r="G9" s="8" t="s">
+        <v>144</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
       <c r="J9" s="10"/>
       <c r="K9" s="9"/>
     </row>
-    <row r="10" spans="1:11" ht="189" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="191.25">
       <c r="A10" s="6" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="52" t="s">
-        <v>123</v>
-      </c>
-      <c r="D10" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" s="54" t="s">
-        <v>295</v>
+        <v>109</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>147</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="G10" s="54" t="s">
-        <v>302</v>
+        <v>113</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>148</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
       <c r="J10" s="10"/>
       <c r="K10" s="9"/>
     </row>
-    <row r="11" spans="1:11" ht="176.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="178.5">
       <c r="A11" s="6" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="52" t="s">
-        <v>124</v>
+        <v>109</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>150</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="E11" s="54" t="s">
-        <v>296</v>
-      </c>
-      <c r="F11" s="53" t="s">
-        <v>273</v>
-      </c>
-      <c r="G11" s="54" t="s">
-        <v>303</v>
+        <v>151</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>153</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="10"/>
       <c r="K11" s="9"/>
     </row>
-    <row r="12" spans="1:11" ht="176.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="178.5">
       <c r="A12" s="6" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="52" t="s">
-        <v>126</v>
+        <v>109</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>155</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="E12" s="52" t="s">
-        <v>289</v>
-      </c>
-      <c r="F12" s="51" t="s">
-        <v>273</v>
-      </c>
-      <c r="G12" s="52" t="s">
-        <v>290</v>
+        <v>151</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>157</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="J12" s="10"/>
       <c r="K12" s="9"/>
     </row>
-    <row r="13" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="51">
       <c r="A13" s="6" t="s">
-        <v>118</v>
+        <v>158</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="D13" s="52" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" s="52" t="s">
-        <v>287</v>
-      </c>
-      <c r="F13" s="51" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="52" t="s">
-        <v>284</v>
+        <v>109</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>162</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
       <c r="J13" s="10"/>
       <c r="K13" s="9"/>
     </row>
-    <row r="14" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="51">
       <c r="A14" s="6" t="s">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="D14" s="52" t="s">
-        <v>125</v>
-      </c>
-      <c r="E14" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="F14" s="51" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="52" t="s">
-        <v>288</v>
+        <v>109</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>166</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
       <c r="J14" s="10"/>
       <c r="K14" s="9"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="45"/>
-      <c r="B15" s="46"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="50"/>
+    <row r="15" spans="1:11">
+      <c r="A15" s="6"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="8"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
       <c r="J15" s="10"/>
       <c r="K15" s="9"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="8"/>
@@ -3144,7 +3194,7 @@
       <c r="J16" s="10"/>
       <c r="K16" s="9"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11">
       <c r="A17" s="6"/>
       <c r="B17" s="7"/>
       <c r="C17" s="8"/>
@@ -3157,7 +3207,7 @@
       <c r="J17" s="10"/>
       <c r="K17" s="9"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11">
       <c r="A18" s="6"/>
       <c r="B18" s="7"/>
       <c r="C18" s="8"/>
@@ -3170,7 +3220,7 @@
       <c r="J18" s="10"/>
       <c r="K18" s="9"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="8"/>
@@ -3183,7 +3233,7 @@
       <c r="J19" s="10"/>
       <c r="K19" s="9"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -3204,93 +3254,93 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5980BF1E-BE4C-4FF8-B6E8-333C3CA090C7}">
   <dimension ref="A1:K38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.21875" customWidth="1"/>
-    <col min="2" max="2" width="16.21875" customWidth="1"/>
-    <col min="3" max="3" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="31.33203125" customWidth="1"/>
-    <col min="6" max="6" width="15.21875" customWidth="1"/>
-    <col min="7" max="7" width="25.88671875" customWidth="1"/>
-    <col min="8" max="8" width="17.109375" customWidth="1"/>
-    <col min="11" max="11" width="11.77734375" customWidth="1"/>
+    <col min="5" max="5" width="31.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" s="11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="75.599999999999994" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="76.5">
       <c r="A2" s="6" t="s">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>297</v>
+        <v>169</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" s="56" t="s">
-        <v>304</v>
-      </c>
-      <c r="F2" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="56" t="s">
-        <v>305</v>
+        <v>53</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>171</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="6"/>
       <c r="J2" s="10"/>
       <c r="K2" s="9"/>
     </row>
-    <row r="3" spans="1:11" ht="75.599999999999994" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="76.5">
       <c r="A3" s="6" t="s">
-        <v>130</v>
+        <v>172</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>131</v>
+        <v>173</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="7"/>
@@ -3300,18 +3350,18 @@
       <c r="J3" s="10"/>
       <c r="K3" s="9"/>
     </row>
-    <row r="4" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="63.75">
       <c r="A4" s="6" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="7"/>
@@ -3321,18 +3371,18 @@
       <c r="J4" s="10"/>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:11" ht="75.599999999999994" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="76.5">
       <c r="A5" s="6" t="s">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="7"/>
@@ -3342,18 +3392,18 @@
       <c r="J5" s="10"/>
       <c r="K5" s="9"/>
     </row>
-    <row r="6" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="102">
       <c r="A6" s="6" t="s">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="7"/>
@@ -3363,18 +3413,18 @@
       <c r="J6" s="10"/>
       <c r="K6" s="9"/>
     </row>
-    <row r="7" spans="1:11" ht="88.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="89.25">
       <c r="A7" s="6" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="7"/>
@@ -3384,18 +3434,18 @@
       <c r="J7" s="10"/>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="51">
       <c r="A8" s="6" t="s">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>141</v>
+        <v>183</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="7"/>
@@ -3405,18 +3455,18 @@
       <c r="J8" s="10"/>
       <c r="K8" s="9"/>
     </row>
-    <row r="9" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="63.75">
       <c r="A9" s="6" t="s">
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>143</v>
+        <v>185</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="7"/>
@@ -3426,18 +3476,18 @@
       <c r="J9" s="10"/>
       <c r="K9" s="9"/>
     </row>
-    <row r="10" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="63.75">
       <c r="A10" s="6" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="7"/>
@@ -3447,18 +3497,18 @@
       <c r="J10" s="10"/>
       <c r="K10" s="9"/>
     </row>
-    <row r="11" spans="1:11" ht="88.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="89.25">
       <c r="A11" s="6" t="s">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="7"/>
@@ -3468,18 +3518,18 @@
       <c r="J11" s="10"/>
       <c r="K11" s="9"/>
     </row>
-    <row r="12" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="63.75">
       <c r="A12" s="6" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="7"/>
@@ -3489,18 +3539,18 @@
       <c r="J12" s="10"/>
       <c r="K12" s="9"/>
     </row>
-    <row r="13" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="51">
       <c r="A13" s="6" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="7"/>
@@ -3510,18 +3560,18 @@
       <c r="J13" s="10"/>
       <c r="K13" s="9"/>
     </row>
-    <row r="14" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="63.75">
       <c r="A14" s="6" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="7"/>
@@ -3531,18 +3581,18 @@
       <c r="J14" s="10"/>
       <c r="K14" s="9"/>
     </row>
-    <row r="15" spans="1:11" ht="88.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="89.25">
       <c r="A15" s="6" t="s">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>155</v>
+        <v>197</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="7"/>
@@ -3552,18 +3602,18 @@
       <c r="J15" s="10"/>
       <c r="K15" s="9"/>
     </row>
-    <row r="16" spans="1:11" ht="75.599999999999994" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="76.5">
       <c r="A16" s="6" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>157</v>
+        <v>199</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="7"/>
@@ -3573,18 +3623,18 @@
       <c r="J16" s="10"/>
       <c r="K16" s="9"/>
     </row>
-    <row r="17" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="63.75">
       <c r="A17" s="6" t="s">
-        <v>158</v>
+        <v>200</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>159</v>
+        <v>201</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="7"/>
@@ -3594,18 +3644,18 @@
       <c r="J17" s="10"/>
       <c r="K17" s="9"/>
     </row>
-    <row r="18" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="51">
       <c r="A18" s="6" t="s">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>161</v>
+        <v>203</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="7"/>
@@ -3615,18 +3665,18 @@
       <c r="J18" s="10"/>
       <c r="K18" s="9"/>
     </row>
-    <row r="19" spans="1:11" ht="75.599999999999994" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="76.5">
       <c r="A19" s="6" t="s">
-        <v>162</v>
+        <v>204</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>163</v>
+        <v>205</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="7"/>
@@ -3636,18 +3686,18 @@
       <c r="J19" s="10"/>
       <c r="K19" s="9"/>
     </row>
-    <row r="20" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="63.75">
       <c r="A20" s="6" t="s">
-        <v>164</v>
+        <v>206</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="7"/>
@@ -3657,18 +3707,18 @@
       <c r="J20" s="10"/>
       <c r="K20" s="9"/>
     </row>
-    <row r="21" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="63.75">
       <c r="A21" s="6" t="s">
-        <v>166</v>
+        <v>208</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>167</v>
+        <v>209</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>168</v>
+        <v>210</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="7"/>
@@ -3678,18 +3728,18 @@
       <c r="J21" s="10"/>
       <c r="K21" s="9"/>
     </row>
-    <row r="22" spans="1:11" ht="75.599999999999994" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="76.5">
       <c r="A22" s="6" t="s">
-        <v>169</v>
+        <v>211</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>170</v>
+        <v>212</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="7"/>
@@ -3699,18 +3749,18 @@
       <c r="J22" s="10"/>
       <c r="K22" s="9"/>
     </row>
-    <row r="23" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="51">
       <c r="A23" s="6" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>172</v>
+        <v>214</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>168</v>
+        <v>210</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="7"/>
@@ -3720,18 +3770,18 @@
       <c r="J23" s="10"/>
       <c r="K23" s="9"/>
     </row>
-    <row r="24" spans="1:11" ht="75.599999999999994" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="76.5">
       <c r="A24" s="6" t="s">
-        <v>173</v>
+        <v>215</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>175</v>
+        <v>217</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="7"/>
@@ -3741,18 +3791,18 @@
       <c r="J24" s="10"/>
       <c r="K24" s="9"/>
     </row>
-    <row r="25" spans="1:11" ht="75.599999999999994" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="76.5">
       <c r="A25" s="6" t="s">
-        <v>176</v>
+        <v>218</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>175</v>
+        <v>217</v>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="7"/>
@@ -3762,18 +3812,18 @@
       <c r="J25" s="10"/>
       <c r="K25" s="9"/>
     </row>
-    <row r="26" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="102">
       <c r="A26" s="6" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>179</v>
+        <v>221</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="7"/>
@@ -3783,18 +3833,18 @@
       <c r="J26" s="10"/>
       <c r="K26" s="9"/>
     </row>
-    <row r="27" spans="1:11" ht="88.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="89.25">
       <c r="A27" s="6" t="s">
-        <v>181</v>
+        <v>223</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>182</v>
+        <v>224</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="7"/>
@@ -3804,18 +3854,18 @@
       <c r="J27" s="10"/>
       <c r="K27" s="9"/>
     </row>
-    <row r="28" spans="1:11" ht="88.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="89.25">
       <c r="A28" s="6" t="s">
-        <v>183</v>
+        <v>225</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="E28" s="8"/>
       <c r="F28" s="7"/>
@@ -3825,18 +3875,18 @@
       <c r="J28" s="10"/>
       <c r="K28" s="9"/>
     </row>
-    <row r="29" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="102">
       <c r="A29" s="6" t="s">
-        <v>185</v>
+        <v>227</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="7"/>
@@ -3846,18 +3896,18 @@
       <c r="J29" s="10"/>
       <c r="K29" s="9"/>
     </row>
-    <row r="30" spans="1:11" ht="75.599999999999994" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="76.5">
       <c r="A30" s="6" t="s">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>188</v>
+        <v>230</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="E30" s="8"/>
       <c r="F30" s="7"/>
@@ -3867,18 +3917,18 @@
       <c r="J30" s="10"/>
       <c r="K30" s="9"/>
     </row>
-    <row r="31" spans="1:11" ht="88.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="89.25">
       <c r="A31" s="6" t="s">
-        <v>189</v>
+        <v>231</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>190</v>
+        <v>232</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="E31" s="8"/>
       <c r="F31" s="7"/>
@@ -3888,18 +3938,18 @@
       <c r="J31" s="10"/>
       <c r="K31" s="9"/>
     </row>
-    <row r="32" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="51">
       <c r="A32" s="6" t="s">
-        <v>191</v>
+        <v>233</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>192</v>
+        <v>234</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="E32" s="8"/>
       <c r="F32" s="7"/>
@@ -3909,18 +3959,18 @@
       <c r="J32" s="10"/>
       <c r="K32" s="9"/>
     </row>
-    <row r="33" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="63.75">
       <c r="A33" s="6" t="s">
-        <v>193</v>
+        <v>235</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>194</v>
+        <v>236</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="E33" s="8"/>
       <c r="F33" s="7"/>
@@ -3930,18 +3980,18 @@
       <c r="J33" s="10"/>
       <c r="K33" s="9"/>
     </row>
-    <row r="34" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" ht="51">
       <c r="A34" s="6" t="s">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="E34" s="8"/>
       <c r="F34" s="7"/>
@@ -3951,18 +4001,18 @@
       <c r="J34" s="10"/>
       <c r="K34" s="9"/>
     </row>
-    <row r="35" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" ht="63.75">
       <c r="A35" s="6" t="s">
-        <v>197</v>
+        <v>239</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>198</v>
+        <v>240</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="E35" s="8"/>
       <c r="F35" s="7"/>
@@ -3972,18 +4022,18 @@
       <c r="J35" s="10"/>
       <c r="K35" s="9"/>
     </row>
-    <row r="36" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="63.75">
       <c r="A36" s="6" t="s">
-        <v>199</v>
+        <v>241</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E36" s="8"/>
       <c r="F36" s="7"/>
@@ -3993,18 +4043,18 @@
       <c r="J36" s="10"/>
       <c r="K36" s="9"/>
     </row>
-    <row r="37" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="63.75">
       <c r="A37" s="6" t="s">
-        <v>201</v>
+        <v>243</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>202</v>
+        <v>244</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E37" s="8"/>
       <c r="F37" s="7"/>
@@ -4014,18 +4064,18 @@
       <c r="J37" s="10"/>
       <c r="K37" s="9"/>
     </row>
-    <row r="38" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" ht="63.75">
       <c r="A38" s="6" t="s">
-        <v>203</v>
+        <v>245</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>204</v>
+        <v>246</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E38" s="8"/>
       <c r="F38" s="7"/>
@@ -4043,59 +4093,59 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC77200-02BE-400F-BDF4-D683FC42DF3F}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" customWidth="1"/>
-    <col min="3" max="3" width="18.88671875" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" customWidth="1"/>
-    <col min="5" max="5" width="18.88671875" customWidth="1"/>
-    <col min="6" max="6" width="14.21875" customWidth="1"/>
-    <col min="7" max="7" width="24.44140625" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" customWidth="1"/>
+    <col min="7" max="7" width="24.42578125" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="11" max="11" width="12.88671875" customWidth="1"/>
+    <col min="11" max="11" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" s="11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="B2" s="27"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="37" t="s">
+        <v>247</v>
+      </c>
+      <c r="B2" s="37"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
       <c r="E2" s="25"/>
@@ -4106,18 +4156,18 @@
       <c r="J2" s="25"/>
       <c r="K2" s="25"/>
     </row>
-    <row r="3" spans="1:11" ht="75.599999999999994" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="76.5">
       <c r="A3" s="6" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="7"/>
@@ -4127,18 +4177,18 @@
       <c r="J3" s="10"/>
       <c r="K3" s="9"/>
     </row>
-    <row r="4" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="63.75">
       <c r="A4" s="6" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="7"/>
@@ -4148,18 +4198,18 @@
       <c r="J4" s="10"/>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:11" ht="88.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="89.25">
       <c r="A5" s="6" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="7"/>
@@ -4169,18 +4219,18 @@
       <c r="J5" s="10"/>
       <c r="K5" s="9"/>
     </row>
-    <row r="6" spans="1:11" ht="88.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="89.25">
       <c r="A6" s="6" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="7"/>
@@ -4190,18 +4240,18 @@
       <c r="J6" s="10"/>
       <c r="K6" s="9"/>
     </row>
-    <row r="7" spans="1:11" ht="75.599999999999994" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="76.5">
       <c r="A7" s="6" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="7"/>
@@ -4211,18 +4261,18 @@
       <c r="J7" s="10"/>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:11" ht="113.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="114.75">
       <c r="A8" s="6" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="7"/>
@@ -4232,18 +4282,18 @@
       <c r="J8" s="10"/>
       <c r="K8" s="9"/>
     </row>
-    <row r="9" spans="1:11" ht="113.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="114.75">
       <c r="A9" s="6" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="7"/>
@@ -4253,18 +4303,18 @@
       <c r="J9" s="10"/>
       <c r="K9" s="9"/>
     </row>
-    <row r="10" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="63.75">
       <c r="A10" s="6" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="7"/>
@@ -4274,18 +4324,18 @@
       <c r="J10" s="10"/>
       <c r="K10" s="9"/>
     </row>
-    <row r="11" spans="1:11" ht="75.599999999999994" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="63.75">
       <c r="A11" s="6" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="7"/>
@@ -4295,18 +4345,18 @@
       <c r="J11" s="10"/>
       <c r="K11" s="9"/>
     </row>
-    <row r="12" spans="1:11" ht="113.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="114.75">
       <c r="A12" s="6" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="7"/>
@@ -4316,18 +4366,18 @@
       <c r="J12" s="10"/>
       <c r="K12" s="9"/>
     </row>
-    <row r="13" spans="1:11" ht="113.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="114.75">
       <c r="A13" s="6" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="7"/>
@@ -4337,18 +4387,18 @@
       <c r="J13" s="10"/>
       <c r="K13" s="9"/>
     </row>
-    <row r="14" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="63.75">
       <c r="A14" s="6" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="7"/>
@@ -4358,18 +4408,18 @@
       <c r="J14" s="10"/>
       <c r="K14" s="9"/>
     </row>
-    <row r="15" spans="1:11" ht="75.599999999999994" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="76.5">
       <c r="A15" s="6" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="7"/>
@@ -4379,18 +4429,18 @@
       <c r="J15" s="10"/>
       <c r="K15" s="9"/>
     </row>
-    <row r="16" spans="1:11" ht="75.599999999999994" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="76.5">
       <c r="A16" s="6" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="7"/>
@@ -4400,18 +4450,18 @@
       <c r="J16" s="10"/>
       <c r="K16" s="9"/>
     </row>
-    <row r="17" spans="1:11" ht="75.599999999999994" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="76.5">
       <c r="A17" s="6" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="7"/>
@@ -4421,18 +4471,18 @@
       <c r="J17" s="10"/>
       <c r="K17" s="9"/>
     </row>
-    <row r="18" spans="1:11" ht="37.799999999999997" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="38.25">
       <c r="A18" s="6" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="7"/>
@@ -4442,18 +4492,18 @@
       <c r="J18" s="10"/>
       <c r="K18" s="9"/>
     </row>
-    <row r="19" spans="1:11" ht="37.799999999999997" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="38.25">
       <c r="A19" s="6" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="7"/>
@@ -4463,18 +4513,18 @@
       <c r="J19" s="10"/>
       <c r="K19" s="9"/>
     </row>
-    <row r="20" spans="1:11" ht="37.799999999999997" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="38.25">
       <c r="A20" s="6" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="7"/>
@@ -4484,18 +4534,18 @@
       <c r="J20" s="10"/>
       <c r="K20" s="9"/>
     </row>
-    <row r="21" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="51">
       <c r="A21" s="6" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="7"/>
@@ -4505,18 +4555,18 @@
       <c r="J21" s="10"/>
       <c r="K21" s="9"/>
     </row>
-    <row r="22" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="63.75">
       <c r="A22" s="6" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="7"/>
@@ -4540,59 +4590,59 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9659557-F3A6-424F-8176-35FE521D3599}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" customWidth="1"/>
-    <col min="7" max="7" width="23.5546875" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" customWidth="1"/>
-    <col min="11" max="11" width="12.21875" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" s="11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="B2" s="27"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="37" t="s">
+        <v>247</v>
+      </c>
+      <c r="B2" s="37"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
       <c r="E2" s="25"/>
@@ -4603,18 +4653,18 @@
       <c r="J2" s="25"/>
       <c r="K2" s="25"/>
     </row>
-    <row r="3" spans="1:11" ht="88.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="89.25">
       <c r="A3" s="6" t="s">
-        <v>205</v>
+        <v>292</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>207</v>
+        <v>294</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>208</v>
+        <v>295</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="7"/>
@@ -4624,18 +4674,18 @@
       <c r="J3" s="10"/>
       <c r="K3" s="9"/>
     </row>
-    <row r="4" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="51">
       <c r="A4" s="6" t="s">
-        <v>209</v>
+        <v>296</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>210</v>
+        <v>297</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="7"/>
@@ -4645,18 +4695,18 @@
       <c r="J4" s="10"/>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="63.75">
       <c r="A5" s="6" t="s">
-        <v>211</v>
+        <v>298</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>212</v>
+        <v>299</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="7"/>
@@ -4666,18 +4716,18 @@
       <c r="J5" s="10"/>
       <c r="K5" s="9"/>
     </row>
-    <row r="6" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="63.75">
       <c r="A6" s="6" t="s">
-        <v>213</v>
+        <v>300</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>214</v>
+        <v>301</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="7"/>
@@ -4687,18 +4737,18 @@
       <c r="J6" s="10"/>
       <c r="K6" s="9"/>
     </row>
-    <row r="7" spans="1:11" ht="75.599999999999994" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="76.5">
       <c r="A7" s="6" t="s">
-        <v>215</v>
+        <v>302</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>216</v>
+        <v>303</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="7"/>
@@ -4708,18 +4758,18 @@
       <c r="J7" s="10"/>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:11" ht="37.799999999999997" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="38.25">
       <c r="A8" s="6" t="s">
-        <v>217</v>
+        <v>304</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>218</v>
+        <v>305</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="7"/>
@@ -4729,18 +4779,18 @@
       <c r="J8" s="10"/>
       <c r="K8" s="9"/>
     </row>
-    <row r="9" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="51">
       <c r="A9" s="6" t="s">
-        <v>219</v>
+        <v>306</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>220</v>
+        <v>307</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="7"/>
@@ -4750,18 +4800,18 @@
       <c r="J9" s="10"/>
       <c r="K9" s="9"/>
     </row>
-    <row r="10" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="63.75">
       <c r="A10" s="6" t="s">
-        <v>221</v>
+        <v>308</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>222</v>
+        <v>309</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="7"/>
@@ -4771,18 +4821,18 @@
       <c r="J10" s="10"/>
       <c r="K10" s="9"/>
     </row>
-    <row r="11" spans="1:11" ht="63" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="63.75">
       <c r="A11" s="6" t="s">
-        <v>223</v>
+        <v>310</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>224</v>
+        <v>311</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="7"/>
